--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238385</v>
+        <v>123238588</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>94869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567546</v>
+        <v>567456</v>
       </c>
       <c r="R2" t="n">
-        <v>6510108</v>
+        <v>6510083</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123222346</v>
+        <v>123223311</v>
       </c>
       <c r="B3" t="n">
-        <v>94869</v>
+        <v>94659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R3" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123222310</v>
+        <v>123238385</v>
       </c>
       <c r="B4" t="n">
-        <v>94865</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567459</v>
+        <v>567546</v>
       </c>
       <c r="R4" t="n">
-        <v>6510087</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,25 +972,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238588</v>
+        <v>123222346</v>
       </c>
       <c r="B5" t="n">
         <v>94869</v>
@@ -1020,23 +1025,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567456</v>
+        <v>567459</v>
       </c>
       <c r="R5" t="n">
-        <v>6510083</v>
+        <v>6510087</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,29 +1075,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123221824</v>
+        <v>123222310</v>
       </c>
       <c r="B6" t="n">
-        <v>94854</v>
+        <v>94865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223311</v>
+        <v>123223361</v>
       </c>
       <c r="B7" t="n">
-        <v>94659</v>
+        <v>94854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567434</v>
+        <v>567433</v>
       </c>
       <c r="R7" t="n">
-        <v>6510147</v>
+        <v>6510154</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123223361</v>
+        <v>123221824</v>
       </c>
       <c r="B8" t="n">
         <v>94854</v>
@@ -1333,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567433</v>
+        <v>567459</v>
       </c>
       <c r="R8" t="n">
-        <v>6510154</v>
+        <v>6510087</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238588</v>
+        <v>123221824</v>
       </c>
       <c r="B2" t="n">
-        <v>94869</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,23 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567456</v>
+        <v>567459</v>
       </c>
       <c r="R2" t="n">
-        <v>6510083</v>
+        <v>6510087</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,29 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123223311</v>
+        <v>123222310</v>
       </c>
       <c r="B3" t="n">
-        <v>94659</v>
+        <v>94865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R3" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238385</v>
+        <v>123223305</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
+        <v>94865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567546</v>
+        <v>567434</v>
       </c>
       <c r="R4" t="n">
-        <v>6510108</v>
+        <v>6510147</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,26 +963,25 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123222346</v>
+        <v>123238588</v>
       </c>
       <c r="B5" t="n">
         <v>94869</v>
@@ -1025,19 +1015,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567459</v>
+        <v>567456</v>
       </c>
       <c r="R5" t="n">
-        <v>6510087</v>
+        <v>6510083</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,28 +1069,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222310</v>
+        <v>123223361</v>
       </c>
       <c r="B6" t="n">
-        <v>94865</v>
+        <v>94854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567459</v>
+        <v>567433</v>
       </c>
       <c r="R6" t="n">
-        <v>6510087</v>
+        <v>6510154</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223361</v>
+        <v>123223311</v>
       </c>
       <c r="B7" t="n">
-        <v>94854</v>
+        <v>94659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567433</v>
+        <v>567434</v>
       </c>
       <c r="R7" t="n">
-        <v>6510154</v>
+        <v>6510147</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123221824</v>
+        <v>123238385</v>
       </c>
       <c r="B8" t="n">
         <v>94854</v>
@@ -1331,19 +1326,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567459</v>
+        <v>567546</v>
       </c>
       <c r="R8" t="n">
-        <v>6510087</v>
+        <v>6510108</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,28 +1380,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123223305</v>
+        <v>123222346</v>
       </c>
       <c r="B9" t="n">
-        <v>94865</v>
+        <v>94869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R9" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123221824</v>
+        <v>123222310</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>94868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123222310</v>
+        <v>123223311</v>
       </c>
       <c r="B3" t="n">
-        <v>94865</v>
+        <v>94662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R3" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123223305</v>
+        <v>123222744</v>
       </c>
       <c r="B4" t="n">
-        <v>94865</v>
+        <v>94857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R4" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238588</v>
+        <v>123238385</v>
       </c>
       <c r="B5" t="n">
-        <v>94869</v>
+        <v>94857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567456</v>
+        <v>567546</v>
       </c>
       <c r="R5" t="n">
-        <v>6510083</v>
+        <v>6510108</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,17 +1081,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123223361</v>
+        <v>123223305</v>
       </c>
       <c r="B6" t="n">
-        <v>94854</v>
+        <v>94868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567433</v>
+        <v>567434</v>
       </c>
       <c r="R6" t="n">
-        <v>6510154</v>
+        <v>6510147</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223311</v>
+        <v>123238588</v>
       </c>
       <c r="B7" t="n">
-        <v>94659</v>
+        <v>94872</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567434</v>
+        <v>567456</v>
       </c>
       <c r="R7" t="n">
-        <v>6510147</v>
+        <v>6510083</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,28 +1278,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123238385</v>
+        <v>123223361</v>
       </c>
       <c r="B8" t="n">
-        <v>94854</v>
+        <v>94857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,23 +1331,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567546</v>
+        <v>567433</v>
       </c>
       <c r="R8" t="n">
-        <v>6510108</v>
+        <v>6510154</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,19 +1381,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1402,7 +1402,7 @@
         <v>123222346</v>
       </c>
       <c r="B9" t="n">
-        <v>94869</v>
+        <v>94872</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222310</v>
+        <v>123223311</v>
       </c>
       <c r="B2" t="n">
-        <v>94868</v>
+        <v>94664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R2" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123223311</v>
+        <v>123222310</v>
       </c>
       <c r="B3" t="n">
-        <v>94662</v>
+        <v>94870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R3" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123222744</v>
+        <v>123221824</v>
       </c>
       <c r="B4" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238385</v>
+        <v>123223361</v>
       </c>
       <c r="B5" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,23 +1015,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567546</v>
+        <v>567433</v>
       </c>
       <c r="R5" t="n">
-        <v>6510108</v>
+        <v>6510154</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,29 +1065,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123223305</v>
+        <v>123238588</v>
       </c>
       <c r="B6" t="n">
-        <v>94868</v>
+        <v>94874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1099,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567434</v>
+        <v>567456</v>
       </c>
       <c r="R6" t="n">
-        <v>6510147</v>
+        <v>6510083</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,28 +1171,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238588</v>
+        <v>123223305</v>
       </c>
       <c r="B7" t="n">
-        <v>94872</v>
+        <v>94870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,41 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567456</v>
+        <v>567434</v>
       </c>
       <c r="R7" t="n">
-        <v>6510083</v>
+        <v>6510147</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,29 +1274,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123223361</v>
+        <v>123238385</v>
       </c>
       <c r="B8" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,19 +1326,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567433</v>
+        <v>567546</v>
       </c>
       <c r="R8" t="n">
-        <v>6510154</v>
+        <v>6510108</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,18 +1380,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Andreas Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1402,7 +1402,7 @@
         <v>123222346</v>
       </c>
       <c r="B9" t="n">
-        <v>94872</v>
+        <v>94874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123223311</v>
+        <v>123223305</v>
       </c>
       <c r="B2" t="n">
-        <v>94664</v>
+        <v>94876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123222310</v>
+        <v>123222346</v>
       </c>
       <c r="B3" t="n">
-        <v>94870</v>
+        <v>94880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123221824</v>
+        <v>123222310</v>
       </c>
       <c r="B4" t="n">
-        <v>94859</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123223361</v>
+        <v>123223311</v>
       </c>
       <c r="B5" t="n">
-        <v>94859</v>
+        <v>94670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567433</v>
+        <v>567434</v>
       </c>
       <c r="R5" t="n">
-        <v>6510154</v>
+        <v>6510147</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238588</v>
+        <v>123223361</v>
       </c>
       <c r="B6" t="n">
-        <v>94874</v>
+        <v>94865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1117,23 +1117,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567456</v>
+        <v>567433</v>
       </c>
       <c r="R6" t="n">
-        <v>6510083</v>
+        <v>6510154</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,29 +1167,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223305</v>
+        <v>123238385</v>
       </c>
       <c r="B7" t="n">
-        <v>94870</v>
+        <v>94865</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1201,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567434</v>
+        <v>567546</v>
       </c>
       <c r="R7" t="n">
-        <v>6510147</v>
+        <v>6510108</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,28 +1273,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123238385</v>
+        <v>123238588</v>
       </c>
       <c r="B8" t="n">
-        <v>94859</v>
+        <v>94880</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567546</v>
+        <v>567456</v>
       </c>
       <c r="R8" t="n">
-        <v>6510108</v>
+        <v>6510083</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Andreas Larsson</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123222346</v>
+        <v>123221824</v>
       </c>
       <c r="B9" t="n">
-        <v>94874</v>
+        <v>94865</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,16 +1415,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123223361</v>
+        <v>123222744</v>
       </c>
       <c r="B2" t="n">
-        <v>94868</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567433</v>
+        <v>567459</v>
       </c>
       <c r="R2" t="n">
-        <v>6510154</v>
+        <v>6510087</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238385</v>
+        <v>123238588</v>
       </c>
       <c r="B3" t="n">
-        <v>94868</v>
+        <v>94900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567546</v>
+        <v>567456</v>
       </c>
       <c r="R3" t="n">
-        <v>6510108</v>
+        <v>6510083</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,17 +877,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123221824</v>
+        <v>123222346</v>
       </c>
       <c r="B4" t="n">
-        <v>94868</v>
+        <v>94900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123223305</v>
+        <v>123238385</v>
       </c>
       <c r="B5" t="n">
-        <v>94879</v>
+        <v>94885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +1002,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567434</v>
+        <v>567546</v>
       </c>
       <c r="R5" t="n">
-        <v>6510147</v>
+        <v>6510108</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,28 +1074,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222310</v>
+        <v>123223305</v>
       </c>
       <c r="B6" t="n">
-        <v>94879</v>
+        <v>94896</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R6" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223311</v>
+        <v>123222310</v>
       </c>
       <c r="B7" t="n">
-        <v>94673</v>
+        <v>94896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R7" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123238588</v>
+        <v>123223361</v>
       </c>
       <c r="B8" t="n">
-        <v>94883</v>
+        <v>94885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1313,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1326,23 +1331,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567456</v>
+        <v>567433</v>
       </c>
       <c r="R8" t="n">
-        <v>6510083</v>
+        <v>6510154</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,29 +1381,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123222346</v>
+        <v>123223311</v>
       </c>
       <c r="B9" t="n">
-        <v>94883</v>
+        <v>94690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R9" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222744</v>
+        <v>123221824</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>94891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238588</v>
+        <v>123223361</v>
       </c>
       <c r="B3" t="n">
-        <v>94900</v>
+        <v>94891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,23 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567456</v>
+        <v>567433</v>
       </c>
       <c r="R3" t="n">
-        <v>6510083</v>
+        <v>6510154</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,29 +861,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123222346</v>
+        <v>123238588</v>
       </c>
       <c r="B4" t="n">
-        <v>94900</v>
+        <v>94906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,19 +913,23 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567459</v>
+        <v>567456</v>
       </c>
       <c r="R4" t="n">
-        <v>6510087</v>
+        <v>6510083</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,28 +967,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238385</v>
+        <v>123222346</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>94906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1020,23 +1020,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567546</v>
+        <v>567459</v>
       </c>
       <c r="R5" t="n">
-        <v>6510108</v>
+        <v>6510087</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,29 +1070,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123223305</v>
+        <v>123238385</v>
       </c>
       <c r="B6" t="n">
-        <v>94896</v>
+        <v>94891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1104,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567434</v>
+        <v>567546</v>
       </c>
       <c r="R6" t="n">
-        <v>6510147</v>
+        <v>6510108</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,18 +1176,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         <v>123222310</v>
       </c>
       <c r="B7" t="n">
-        <v>94896</v>
+        <v>94902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123223361</v>
+        <v>123223311</v>
       </c>
       <c r="B8" t="n">
-        <v>94885</v>
+        <v>94696</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567433</v>
+        <v>567434</v>
       </c>
       <c r="R8" t="n">
-        <v>6510154</v>
+        <v>6510147</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123223311</v>
+        <v>123223305</v>
       </c>
       <c r="B9" t="n">
-        <v>94690</v>
+        <v>94902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123221824</v>
+        <v>123238588</v>
       </c>
       <c r="B2" t="n">
-        <v>94891</v>
+        <v>94908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567459</v>
+        <v>567456</v>
       </c>
       <c r="R2" t="n">
-        <v>6510087</v>
+        <v>6510083</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,28 +763,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123223361</v>
+        <v>123222744</v>
       </c>
       <c r="B3" t="n">
-        <v>94891</v>
+        <v>94893</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567433</v>
+        <v>567459</v>
       </c>
       <c r="R3" t="n">
-        <v>6510154</v>
+        <v>6510087</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238588</v>
+        <v>123222310</v>
       </c>
       <c r="B4" t="n">
-        <v>94906</v>
+        <v>94904</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,41 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567456</v>
+        <v>567459</v>
       </c>
       <c r="R4" t="n">
-        <v>6510083</v>
+        <v>6510087</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,29 +968,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123222346</v>
+        <v>123223311</v>
       </c>
       <c r="B5" t="n">
-        <v>94906</v>
+        <v>94698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R5" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1091,7 +1091,7 @@
         <v>123238385</v>
       </c>
       <c r="B6" t="n">
-        <v>94891</v>
+        <v>94893</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123222310</v>
+        <v>123223361</v>
       </c>
       <c r="B7" t="n">
-        <v>94902</v>
+        <v>94893</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567459</v>
+        <v>567433</v>
       </c>
       <c r="R7" t="n">
-        <v>6510087</v>
+        <v>6510154</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123223311</v>
+        <v>123222346</v>
       </c>
       <c r="B8" t="n">
-        <v>94696</v>
+        <v>94908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567434</v>
+        <v>567459</v>
       </c>
       <c r="R8" t="n">
-        <v>6510147</v>
+        <v>6510087</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1402,7 +1402,7 @@
         <v>123223305</v>
       </c>
       <c r="B9" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238588</v>
+        <v>123223361</v>
       </c>
       <c r="B2" t="n">
-        <v>94908</v>
+        <v>95401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,23 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567456</v>
+        <v>567433</v>
       </c>
       <c r="R2" t="n">
-        <v>6510083</v>
+        <v>6510154</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,19 +759,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +780,7 @@
         <v>123222744</v>
       </c>
       <c r="B3" t="n">
-        <v>94893</v>
+        <v>95401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123222310</v>
+        <v>123238588</v>
       </c>
       <c r="B4" t="n">
-        <v>94904</v>
+        <v>95416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +895,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567459</v>
+        <v>567456</v>
       </c>
       <c r="R4" t="n">
-        <v>6510087</v>
+        <v>6510083</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,28 +967,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123223311</v>
+        <v>123238385</v>
       </c>
       <c r="B5" t="n">
-        <v>94698</v>
+        <v>95401</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +1002,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567434</v>
+        <v>567546</v>
       </c>
       <c r="R5" t="n">
-        <v>6510147</v>
+        <v>6510108</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,28 +1074,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238385</v>
+        <v>123222346</v>
       </c>
       <c r="B6" t="n">
-        <v>94893</v>
+        <v>95416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,16 +1109,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1122,23 +1127,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567546</v>
+        <v>567459</v>
       </c>
       <c r="R6" t="n">
-        <v>6510108</v>
+        <v>6510087</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,29 +1177,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123223361</v>
+        <v>123222310</v>
       </c>
       <c r="B7" t="n">
-        <v>94893</v>
+        <v>95412</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567433</v>
+        <v>567459</v>
       </c>
       <c r="R7" t="n">
-        <v>6510154</v>
+        <v>6510087</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123222346</v>
+        <v>123223311</v>
       </c>
       <c r="B8" t="n">
-        <v>94908</v>
+        <v>95206</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567459</v>
+        <v>567434</v>
       </c>
       <c r="R8" t="n">
-        <v>6510087</v>
+        <v>6510147</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1402,7 +1402,7 @@
         <v>123223305</v>
       </c>
       <c r="B9" t="n">
-        <v>94904</v>
+        <v>95412</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131236926</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131236926</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131236926</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131236926</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131236926</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>131289566</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1719,7 +1719,7 @@
         <v>131528178</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -1828,7 +1828,7 @@
         <v>133695480</v>
       </c>
       <c r="B13" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123223361</v>
+        <v>123220975</v>
       </c>
       <c r="B2" t="n">
-        <v>95401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567433</v>
+        <v>567466</v>
       </c>
       <c r="R2" t="n">
-        <v>6510154</v>
+        <v>6510055</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123222744</v>
+        <v>123222310</v>
       </c>
       <c r="B3" t="n">
-        <v>95401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238588</v>
+        <v>123223305</v>
       </c>
       <c r="B4" t="n">
-        <v>95416</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,41 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567456</v>
+        <v>567434</v>
       </c>
       <c r="R4" t="n">
-        <v>6510083</v>
+        <v>6510147</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,34 +948,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238385</v>
+        <v>123222346</v>
       </c>
       <c r="B5" t="n">
-        <v>95401</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1020,23 +995,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567546</v>
+        <v>567459</v>
       </c>
       <c r="R5" t="n">
-        <v>6510108</v>
+        <v>6510087</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,34 +1045,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222346</v>
+        <v>123238588</v>
       </c>
       <c r="B6" t="n">
-        <v>95416</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,19 +1092,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567459</v>
+        <v>567456</v>
       </c>
       <c r="R6" t="n">
-        <v>6510087</v>
+        <v>6510083</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,33 +1146,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123222310</v>
+        <v>123221824</v>
       </c>
       <c r="B7" t="n">
-        <v>95412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123223311</v>
+        <v>123223361</v>
       </c>
       <c r="B8" t="n">
-        <v>95206</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567434</v>
+        <v>567433</v>
       </c>
       <c r="R8" t="n">
-        <v>6510147</v>
+        <v>6510154</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1399,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123223305</v>
+        <v>123238385</v>
       </c>
       <c r="B9" t="n">
-        <v>95412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,37 +1370,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkliden, Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567434</v>
+        <v>567546</v>
       </c>
       <c r="R9" t="n">
-        <v>6510147</v>
+        <v>6510108</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,74 +1442,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Lena Lundin Johansson, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131236926</v>
+        <v>123223311</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>96231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydost Björkliden, Ög</t>
+          <t>Björkliden, Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567473</v>
+        <v>567434</v>
       </c>
       <c r="R10" t="n">
-        <v>6510086</v>
+        <v>6510147</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,17 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera grova aspar lämpliga för bobygge i anslutning. Varav åtminstone två med äldre bohål.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,26 +1546,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131289566</v>
+        <v>131236926</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1644,20 +1591,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strax öster om Björkliden, Ög</t>
+          <t>Sydost Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567450</v>
+        <v>567473</v>
       </c>
       <c r="R11" t="n">
-        <v>6510180</v>
+        <v>6510086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,12 +1631,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera grova aspar lämpliga för bobygge i anslutning. Varav åtminstone två med äldre bohål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1716,14 +1668,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131528178</v>
+        <v>131289566</v>
       </c>
       <c r="B12" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1746,30 +1698,26 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sydost Björkliden, Ög</t>
+          <t>Strax öster om Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567538</v>
+        <v>567450</v>
       </c>
       <c r="R12" t="n">
-        <v>6510102</v>
+        <v>6510180</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1793,12 +1741,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,10 +1773,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133695480</v>
+        <v>131528178</v>
       </c>
       <c r="B13" t="n">
-        <v>101396</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,45 +1784,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Björkliden, Ög</t>
+          <t>Sydost Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567470</v>
+        <v>567538</v>
       </c>
       <c r="R13" t="n">
-        <v>6510067</v>
+        <v>6510102</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,12 +1850,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,7 +1864,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1928,6 +1879,112 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133695480</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567470</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6510067</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11100-2025 artfynd.xlsx
+++ b/artfynd/A 11100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123220975</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123223305</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222346</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123221824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123223361</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238385</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123223311</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131236926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1770,6 +1825,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131289566</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131528178</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,8 +2050,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133695480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>